--- a/Data/LittRu_matrix_all_extended.xlsx
+++ b/Data/LittRu_matrix_all_extended.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6f65c9cc82766c5b/Documents/_Post-Bac-Python/Programs (LittRu - Publication 01.07.2026)/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6f65c9cc82766c5b/Documents/_Post-Bac-Python/Programs (LittRu - Publication 2026.07.15)/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05F92C20-07EC-4126-8B1A-86D5D22CAF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{05F92C20-07EC-4126-8B1A-86D5D22CAF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9EBAF96-738C-453D-8F9E-4EDB14ABE74D}"/>
   <bookViews>
-    <workbookView xWindow="-25905" yWindow="3345" windowWidth="24150" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1455" yWindow="1785" windowWidth="24150" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="330">
   <si>
     <t>Works</t>
   </si>
@@ -745,9 +745,6 @@
     <t>La Vie d'Arséniev</t>
   </si>
   <si>
-    <t>La Vie de l'Archiprêtre Avvakum</t>
-  </si>
-  <si>
     <t>La Vie de Klim Samguine</t>
   </si>
   <si>
@@ -1612,7 +1609,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C2">
         <v>1904</v>
@@ -1621,19 +1618,19 @@
         <v>1936</v>
       </c>
       <c r="E2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F2">
         <v>1933</v>
       </c>
       <c r="G2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1836,7 +1833,7 @@
         <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C3">
         <v>1821</v>
@@ -1845,19 +1842,19 @@
         <v>1881</v>
       </c>
       <c r="E3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F3">
         <v>1875</v>
       </c>
       <c r="G3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -2060,28 +2057,28 @@
         <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C4">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D4">
         <v>1936</v>
       </c>
       <c r="E4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F4">
         <v>1925</v>
       </c>
       <c r="G4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2284,7 +2281,7 @@
         <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C5">
         <v>1811</v>
@@ -2293,19 +2290,19 @@
         <v>1852</v>
       </c>
       <c r="E5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F5">
         <v>1839</v>
       </c>
       <c r="G5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2508,7 +2505,7 @@
         <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C6">
         <v>1828</v>
@@ -2517,19 +2514,19 @@
         <v>1910</v>
       </c>
       <c r="E6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F6">
         <v>1875</v>
       </c>
       <c r="G6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -2732,7 +2729,7 @@
         <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C7">
         <v>1892</v>
@@ -2741,19 +2738,19 @@
         <v>1968</v>
       </c>
       <c r="E7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F7">
         <v>1946</v>
       </c>
       <c r="G7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2956,7 +2953,7 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>1918</v>
@@ -2965,19 +2962,19 @@
         <v>2008</v>
       </c>
       <c r="E8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F8">
         <v>1970</v>
       </c>
       <c r="G8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3180,7 +3177,7 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9">
         <v>1812</v>
@@ -3189,19 +3186,19 @@
         <v>1870</v>
       </c>
       <c r="E9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F9">
         <v>1844</v>
       </c>
       <c r="G9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -3404,7 +3401,7 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C10">
         <v>1929</v>
@@ -3413,19 +3410,19 @@
         <v>1979</v>
       </c>
       <c r="E10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F10">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="G10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3628,7 +3625,7 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C11">
         <v>1860</v>
@@ -3637,19 +3634,19 @@
         <v>1904</v>
       </c>
       <c r="E11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F11">
         <v>1889</v>
       </c>
       <c r="G11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3852,28 +3849,28 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C12">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D12">
         <v>1936</v>
       </c>
       <c r="E12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F12">
         <v>1902</v>
       </c>
       <c r="G12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4076,7 +4073,7 @@
         <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C13">
         <v>1899</v>
@@ -4085,19 +4082,19 @@
         <v>1994</v>
       </c>
       <c r="E13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F13">
         <v>1924</v>
       </c>
       <c r="G13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4300,7 +4297,7 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C14">
         <v>1828</v>
@@ -4309,19 +4306,19 @@
         <v>1910</v>
       </c>
       <c r="E14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F14">
         <v>1859</v>
       </c>
       <c r="G14" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I14" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -4524,7 +4521,7 @@
         <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C15">
         <v>1799</v>
@@ -4533,19 +4530,19 @@
         <v>1837</v>
       </c>
       <c r="E15" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F15">
         <v>1825</v>
       </c>
       <c r="G15" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -4748,7 +4745,7 @@
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C16">
         <v>1745</v>
@@ -4757,19 +4754,19 @@
         <v>1792</v>
       </c>
       <c r="E16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F16">
         <v>1769</v>
       </c>
       <c r="G16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -4972,7 +4969,7 @@
         <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C17">
         <v>1818</v>
@@ -4981,19 +4978,19 @@
         <v>1883</v>
       </c>
       <c r="E17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F17">
         <v>1850</v>
       </c>
       <c r="G17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -5196,7 +5193,7 @@
         <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C18">
         <v>1894</v>
@@ -5205,19 +5202,19 @@
         <v>1941</v>
       </c>
       <c r="E18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F18">
         <v>1925</v>
       </c>
       <c r="G18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I18" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -5420,7 +5417,7 @@
         <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C19">
         <v>1799</v>
@@ -5429,19 +5426,19 @@
         <v>1837</v>
       </c>
       <c r="E19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F19">
         <v>1833</v>
       </c>
       <c r="G19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -5644,7 +5641,7 @@
         <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C20">
         <v>1860</v>
@@ -5653,19 +5650,19 @@
         <v>1904</v>
       </c>
       <c r="E20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F20">
         <v>1904</v>
       </c>
       <c r="G20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -5868,7 +5865,7 @@
         <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C21">
         <v>1903</v>
@@ -5877,19 +5874,19 @@
         <v>1972</v>
       </c>
       <c r="E21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F21">
         <v>1944</v>
       </c>
       <c r="G21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -6092,7 +6089,7 @@
         <v>94</v>
       </c>
       <c r="B22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C22">
         <v>1882</v>
@@ -6101,19 +6098,19 @@
         <v>1945</v>
       </c>
       <c r="E22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F22">
         <v>1931</v>
       </c>
       <c r="G22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -6316,7 +6313,7 @@
         <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C23">
         <v>1799</v>
@@ -6325,19 +6322,19 @@
         <v>1837</v>
       </c>
       <c r="E23" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F23">
         <v>1830</v>
       </c>
       <c r="G23" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -6540,7 +6537,7 @@
         <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24">
         <v>1929</v>
@@ -6549,19 +6546,19 @@
         <v>1979</v>
       </c>
       <c r="E24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F24">
         <v>1964</v>
       </c>
       <c r="G24" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I24" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -6764,7 +6761,7 @@
         <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25">
         <v>1812</v>
@@ -6773,19 +6770,19 @@
         <v>1870</v>
       </c>
       <c r="E25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F25">
         <v>1860</v>
       </c>
       <c r="G25" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I25" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -6988,7 +6985,7 @@
         <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C26">
         <v>1791</v>
@@ -6997,19 +6994,19 @@
         <v>1859</v>
       </c>
       <c r="E26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F26">
         <v>1856</v>
       </c>
       <c r="G26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -7212,7 +7209,7 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C27">
         <v>1891</v>
@@ -7221,19 +7218,19 @@
         <v>1940</v>
       </c>
       <c r="E27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F27">
         <v>1925</v>
       </c>
       <c r="G27" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H27" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I27" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -7436,7 +7433,7 @@
         <v>100</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C28">
         <v>1900</v>
@@ -7445,19 +7442,19 @@
         <v>1962</v>
       </c>
       <c r="E28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F28">
         <v>1960</v>
       </c>
       <c r="G28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -7660,7 +7657,7 @@
         <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C29">
         <v>1799</v>
@@ -7669,19 +7666,19 @@
         <v>1837</v>
       </c>
       <c r="E29" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F29">
         <v>1830</v>
       </c>
       <c r="G29" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I29" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -7884,7 +7881,7 @@
         <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C30">
         <v>1828</v>
@@ -7893,19 +7890,19 @@
         <v>1910</v>
       </c>
       <c r="E30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F30">
         <v>1858</v>
       </c>
       <c r="G30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H30" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -8108,7 +8105,7 @@
         <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C31">
         <v>1799</v>
@@ -8117,19 +8114,19 @@
         <v>1837</v>
       </c>
       <c r="E31" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F31">
         <v>1830</v>
       </c>
       <c r="G31" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I31" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -8332,7 +8329,7 @@
         <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C32">
         <v>1821</v>
@@ -8341,19 +8338,19 @@
         <v>1881</v>
       </c>
       <c r="E32" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F32">
         <v>1866</v>
       </c>
       <c r="G32" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H32" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I32" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -8556,7 +8553,7 @@
         <v>105</v>
       </c>
       <c r="B33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C33">
         <v>1860</v>
@@ -8565,19 +8562,19 @@
         <v>1904</v>
       </c>
       <c r="E33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F33">
         <v>1899</v>
       </c>
       <c r="G33" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I33" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -8780,7 +8777,7 @@
         <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C34">
         <v>1799</v>
@@ -8789,19 +8786,19 @@
         <v>1837</v>
       </c>
       <c r="E34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F34">
         <v>1834</v>
       </c>
       <c r="G34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H34" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I34" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -9004,7 +9001,7 @@
         <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C35">
         <v>1819</v>
@@ -9013,19 +9010,19 @@
         <v>1883</v>
       </c>
       <c r="E35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F35">
         <v>1875</v>
       </c>
       <c r="G35" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H35" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I35" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -9228,7 +9225,7 @@
         <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C36">
         <v>1911</v>
@@ -9237,19 +9234,19 @@
         <v>1987</v>
       </c>
       <c r="E36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F36">
         <v>1946</v>
       </c>
       <c r="G36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H36" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I36" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -9452,7 +9449,7 @@
         <v>109</v>
       </c>
       <c r="B37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C37">
         <v>1863</v>
@@ -9461,19 +9458,19 @@
         <v>1927</v>
       </c>
       <c r="E37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F37">
         <v>1902</v>
       </c>
       <c r="G37" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H37" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I37" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -9676,7 +9673,7 @@
         <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C38">
         <v>1821</v>
@@ -9685,19 +9682,19 @@
         <v>1881</v>
       </c>
       <c r="E38" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F38">
         <v>1871</v>
       </c>
       <c r="G38" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H38" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -9900,7 +9897,7 @@
         <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C39">
         <v>1905</v>
@@ -9909,19 +9906,19 @@
         <v>1984</v>
       </c>
       <c r="E39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F39">
         <v>1957</v>
       </c>
       <c r="G39" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H39" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I39" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -10124,7 +10121,7 @@
         <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C40">
         <v>1890</v>
@@ -10133,19 +10130,19 @@
         <v>1960</v>
       </c>
       <c r="E40" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F40">
         <v>1954</v>
       </c>
       <c r="G40" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H40" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -10348,7 +10345,7 @@
         <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C41">
         <v>1905</v>
@@ -10357,19 +10354,19 @@
         <v>1984</v>
       </c>
       <c r="E41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F41">
         <v>1934</v>
       </c>
       <c r="G41" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I41" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -10572,7 +10569,7 @@
         <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C42">
         <v>1799</v>
@@ -10581,19 +10578,19 @@
         <v>1837</v>
       </c>
       <c r="E42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F42">
         <v>1833</v>
       </c>
       <c r="G42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H42" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -10796,7 +10793,7 @@
         <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C43">
         <v>1821</v>
@@ -10805,19 +10802,19 @@
         <v>1881</v>
       </c>
       <c r="E43" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F43">
         <v>1876</v>
       </c>
       <c r="G43" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H43" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I43" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -11020,7 +11017,7 @@
         <v>116</v>
       </c>
       <c r="B44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C44">
         <v>1880</v>
@@ -11029,19 +11026,19 @@
         <v>1921</v>
       </c>
       <c r="E44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F44">
         <v>1918</v>
       </c>
       <c r="G44" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I44" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -11244,7 +11241,7 @@
         <v>117</v>
       </c>
       <c r="B45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C45">
         <v>1897</v>
@@ -11253,19 +11250,19 @@
         <v>1942</v>
       </c>
       <c r="E45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F45">
         <v>1928</v>
       </c>
       <c r="G45" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I45" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -11468,7 +11465,7 @@
         <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C46">
         <v>1870</v>
@@ -11477,19 +11474,19 @@
         <v>1938</v>
       </c>
       <c r="E46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F46">
         <v>1905</v>
       </c>
       <c r="G46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H46" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I46" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -11692,28 +11689,28 @@
         <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C47">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D47">
         <v>1936</v>
       </c>
       <c r="E47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F47">
         <v>1912</v>
       </c>
       <c r="G47" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H47" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I47" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -11916,7 +11913,7 @@
         <v>120</v>
       </c>
       <c r="B48" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C48">
         <v>1828</v>
@@ -11925,19 +11922,19 @@
         <v>1910</v>
       </c>
       <c r="E48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F48">
         <v>1853</v>
       </c>
       <c r="G48" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H48" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -12140,7 +12137,7 @@
         <v>121</v>
       </c>
       <c r="B49" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C49">
         <v>1904</v>
@@ -12149,19 +12146,19 @@
         <v>1936</v>
       </c>
       <c r="E49" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F49">
         <v>1936</v>
       </c>
       <c r="G49" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H49" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -12364,28 +12361,28 @@
         <v>122</v>
       </c>
       <c r="B50" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C50">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D50">
         <v>1936</v>
       </c>
       <c r="E50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F50">
         <v>1914</v>
       </c>
       <c r="G50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H50" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -12588,28 +12585,28 @@
         <v>123</v>
       </c>
       <c r="B51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C51">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D51">
         <v>1936</v>
       </c>
       <c r="E51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F51">
         <v>1906</v>
       </c>
       <c r="G51" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H51" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I51" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -12812,7 +12809,7 @@
         <v>124</v>
       </c>
       <c r="B52" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C52">
         <v>1892</v>
@@ -12821,19 +12818,19 @@
         <v>1968</v>
       </c>
       <c r="E52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F52">
         <v>1956</v>
       </c>
       <c r="G52" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H52" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I52" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -13036,7 +13033,7 @@
         <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C53">
         <v>1892</v>
@@ -13045,19 +13042,19 @@
         <v>1977</v>
       </c>
       <c r="E53" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F53">
         <v>1948</v>
       </c>
       <c r="G53" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H53" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I53" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -13260,7 +13257,7 @@
         <v>126</v>
       </c>
       <c r="B54" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C54">
         <v>1821</v>
@@ -13269,19 +13266,19 @@
         <v>1881</v>
       </c>
       <c r="E54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F54">
         <v>1870</v>
       </c>
       <c r="G54" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H54" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I54" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -13484,7 +13481,7 @@
         <v>127</v>
       </c>
       <c r="B55" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C55">
         <v>1910</v>
@@ -13493,19 +13490,19 @@
         <v>1975</v>
       </c>
       <c r="E55" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F55">
         <v>1957</v>
       </c>
       <c r="G55" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H55" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I55" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -13708,7 +13705,7 @@
         <v>128</v>
       </c>
       <c r="B56" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C56">
         <v>1799</v>
@@ -13717,19 +13714,19 @@
         <v>1837</v>
       </c>
       <c r="E56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F56">
         <v>1827</v>
       </c>
       <c r="G56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -13932,7 +13929,7 @@
         <v>129</v>
       </c>
       <c r="B57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C57">
         <v>1860</v>
@@ -13941,19 +13938,19 @@
         <v>1904</v>
       </c>
       <c r="E57" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F57">
         <v>1902</v>
       </c>
       <c r="G57" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H57" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I57" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -14156,7 +14153,7 @@
         <v>130</v>
       </c>
       <c r="B58" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C58">
         <v>1831</v>
@@ -14165,19 +14162,19 @@
         <v>1895</v>
       </c>
       <c r="E58" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F58">
         <v>1874</v>
       </c>
       <c r="G58" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H58" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I58" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -14380,7 +14377,7 @@
         <v>131</v>
       </c>
       <c r="B59" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C59">
         <v>1799</v>
@@ -14389,19 +14386,19 @@
         <v>1837</v>
       </c>
       <c r="E59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F59">
         <v>1836</v>
       </c>
       <c r="G59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I59" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -14604,7 +14601,7 @@
         <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C60">
         <v>1923</v>
@@ -14613,19 +14610,19 @@
         <v>1983</v>
       </c>
       <c r="E60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F60">
         <v>1956</v>
       </c>
       <c r="G60" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H60" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I60" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -14828,7 +14825,7 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C61">
         <v>1821</v>
@@ -14837,19 +14834,19 @@
         <v>1881</v>
       </c>
       <c r="E61" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F61">
         <v>1880</v>
       </c>
       <c r="G61" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H61" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I61" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -15052,7 +15049,7 @@
         <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C62">
         <v>1818</v>
@@ -15061,19 +15058,19 @@
         <v>1883</v>
       </c>
       <c r="E62" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F62">
         <v>1867</v>
       </c>
       <c r="G62" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H62" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I62" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -15276,7 +15273,7 @@
         <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C63">
         <v>1891</v>
@@ -15285,19 +15282,19 @@
         <v>1940</v>
       </c>
       <c r="E63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F63">
         <v>1924</v>
       </c>
       <c r="G63" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I63" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -15500,7 +15497,7 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C64">
         <v>1821</v>
@@ -15509,19 +15506,19 @@
         <v>1878</v>
       </c>
       <c r="E64" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F64">
         <v>1863</v>
       </c>
       <c r="G64" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H64" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I64" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -15724,7 +15721,7 @@
         <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C65">
         <v>1826</v>
@@ -15733,19 +15730,19 @@
         <v>1889</v>
       </c>
       <c r="E65" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F65">
         <v>1876</v>
       </c>
       <c r="G65" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H65" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I65" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -15948,7 +15945,7 @@
         <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C66">
         <v>1931</v>
@@ -15957,19 +15954,19 @@
         <v>2003</v>
       </c>
       <c r="E66" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F66">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="G66" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H66" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I66" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -16172,7 +16169,7 @@
         <v>139</v>
       </c>
       <c r="B67" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C67">
         <v>1828</v>
@@ -16181,19 +16178,19 @@
         <v>1910</v>
       </c>
       <c r="E67" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F67">
         <v>1866</v>
       </c>
       <c r="G67" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H67" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I67" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -16396,7 +16393,7 @@
         <v>140</v>
       </c>
       <c r="B68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C68">
         <v>1828</v>
@@ -16405,19 +16402,19 @@
         <v>1910</v>
       </c>
       <c r="E68" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F68">
         <v>1900</v>
       </c>
       <c r="G68" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H68" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I68" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -16620,7 +16617,7 @@
         <v>141</v>
       </c>
       <c r="B69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C69">
         <v>1814</v>
@@ -16629,19 +16626,19 @@
         <v>1841</v>
       </c>
       <c r="E69" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F69">
         <v>1840</v>
       </c>
       <c r="G69" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H69" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I69" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -16844,7 +16841,7 @@
         <v>142</v>
       </c>
       <c r="B70" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C70">
         <v>1826</v>
@@ -16853,19 +16850,19 @@
         <v>1889</v>
       </c>
       <c r="E70" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F70">
         <v>1870</v>
       </c>
       <c r="G70" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H70" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I70" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -17068,7 +17065,7 @@
         <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C71">
         <v>1918</v>
@@ -17077,19 +17074,19 @@
         <v>1998</v>
       </c>
       <c r="E71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F71">
         <v>1956</v>
       </c>
       <c r="G71" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H71" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I71" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -17292,7 +17289,7 @@
         <v>144</v>
       </c>
       <c r="B72" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72">
         <v>1908</v>
@@ -17301,19 +17298,19 @@
         <v>1981</v>
       </c>
       <c r="E72" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F72">
         <v>1946</v>
       </c>
       <c r="G72" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H72" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I72" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -17516,7 +17513,7 @@
         <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C73">
         <v>1821</v>
@@ -17525,19 +17522,19 @@
         <v>1881</v>
       </c>
       <c r="E73" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F73">
         <v>1861</v>
       </c>
       <c r="G73" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H73" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I73" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -17740,7 +17737,7 @@
         <v>146</v>
       </c>
       <c r="B74" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C74">
         <v>1811</v>
@@ -17749,19 +17746,19 @@
         <v>1852</v>
       </c>
       <c r="E74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F74">
         <v>1837</v>
       </c>
       <c r="G74" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H74" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I74" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -17964,7 +17961,7 @@
         <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C75">
         <v>1923</v>
@@ -17973,19 +17970,19 @@
         <v>1983</v>
       </c>
       <c r="E75" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F75">
         <v>1958</v>
       </c>
       <c r="G75" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H75" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -18188,7 +18185,7 @@
         <v>148</v>
       </c>
       <c r="B76" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C76">
         <v>1821</v>
@@ -18197,19 +18194,19 @@
         <v>1881</v>
       </c>
       <c r="E76" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F76">
         <v>1869</v>
       </c>
       <c r="G76" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H76" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I76" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -18412,7 +18409,7 @@
         <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C77">
         <v>1928</v>
@@ -18421,19 +18418,19 @@
         <v>2008</v>
       </c>
       <c r="E77" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F77">
         <v>1970</v>
       </c>
       <c r="G77" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H77" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -18636,7 +18633,7 @@
         <v>150</v>
       </c>
       <c r="B78" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C78">
         <v>1918</v>
@@ -18645,19 +18642,19 @@
         <v>2008</v>
       </c>
       <c r="E78" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F78">
         <v>1963</v>
       </c>
       <c r="G78" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H78" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I78" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -18860,7 +18857,7 @@
         <v>151</v>
       </c>
       <c r="B79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C79">
         <v>1860</v>
@@ -18869,19 +18866,19 @@
         <v>1904</v>
       </c>
       <c r="E79" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F79">
         <v>1888</v>
       </c>
       <c r="G79" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H79" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I79" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -19084,7 +19081,7 @@
         <v>152</v>
       </c>
       <c r="B80" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C80">
         <v>1791</v>
@@ -19093,19 +19090,19 @@
         <v>1859</v>
       </c>
       <c r="E80" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F80">
         <v>1856</v>
       </c>
       <c r="G80" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H80" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I80" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -19308,7 +19305,7 @@
         <v>153</v>
       </c>
       <c r="B81" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C81">
         <v>1901</v>
@@ -19317,19 +19314,19 @@
         <v>1956</v>
       </c>
       <c r="E81" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F81">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="G81" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H81" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I81" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -19532,7 +19529,7 @@
         <v>154</v>
       </c>
       <c r="B82" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C82">
         <v>1892</v>
@@ -19541,19 +19538,19 @@
         <v>1968</v>
       </c>
       <c r="E82" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F82">
         <v>1954</v>
       </c>
       <c r="G82" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H82" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I82" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J82">
         <v>1</v>
@@ -19756,7 +19753,7 @@
         <v>155</v>
       </c>
       <c r="B83" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C83">
         <v>1821</v>
@@ -19765,19 +19762,19 @@
         <v>1881</v>
       </c>
       <c r="E83" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F83">
         <v>1866</v>
       </c>
       <c r="G83" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H83" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I83" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J83">
         <v>1</v>
@@ -19980,7 +19977,7 @@
         <v>156</v>
       </c>
       <c r="B84" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C84">
         <v>1811</v>
@@ -19989,19 +19986,19 @@
         <v>1852</v>
       </c>
       <c r="E84" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F84">
         <v>1835</v>
       </c>
       <c r="G84" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H84" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I84" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -20204,7 +20201,7 @@
         <v>157</v>
       </c>
       <c r="B85" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C85">
         <v>1918</v>
@@ -20213,19 +20210,19 @@
         <v>2008</v>
       </c>
       <c r="E85" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F85">
         <v>1962</v>
       </c>
       <c r="G85" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H85" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I85" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -20428,7 +20425,7 @@
         <v>158</v>
       </c>
       <c r="B86" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C86">
         <v>1915</v>
@@ -20437,19 +20434,19 @@
         <v>1979</v>
       </c>
       <c r="E86" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F86">
         <v>1944</v>
       </c>
       <c r="G86" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H86" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I86" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -20652,7 +20649,7 @@
         <v>159</v>
       </c>
       <c r="B87" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C87">
         <v>1923</v>
@@ -20661,19 +20658,19 @@
         <v>1983</v>
       </c>
       <c r="E87" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F87">
         <v>1961</v>
       </c>
       <c r="G87" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H87" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I87" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -20876,7 +20873,7 @@
         <v>160</v>
       </c>
       <c r="B88" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C88">
         <v>1911</v>
@@ -20885,19 +20882,19 @@
         <v>1987</v>
       </c>
       <c r="E88" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F88">
         <v>1962</v>
       </c>
       <c r="G88" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H88" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I88" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J88">
         <v>1</v>
@@ -21100,7 +21097,7 @@
         <v>161</v>
       </c>
       <c r="B89" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C89">
         <v>1831</v>
@@ -21109,19 +21106,19 @@
         <v>1895</v>
       </c>
       <c r="E89" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F89">
         <v>1865</v>
       </c>
       <c r="G89" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H89" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I89" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -21324,7 +21321,7 @@
         <v>162</v>
       </c>
       <c r="B90" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C90">
         <v>1894</v>
@@ -21333,19 +21330,19 @@
         <v>1943</v>
       </c>
       <c r="E90" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F90">
         <v>1928</v>
       </c>
       <c r="G90" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H90" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I90" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -21548,7 +21545,7 @@
         <v>163</v>
       </c>
       <c r="B91" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C91">
         <v>1918</v>
@@ -21557,19 +21554,19 @@
         <v>2008</v>
       </c>
       <c r="E91" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F91">
         <v>1963</v>
       </c>
       <c r="G91" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H91" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I91" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -21772,7 +21769,7 @@
         <v>164</v>
       </c>
       <c r="B92" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C92">
         <v>1891</v>
@@ -21781,19 +21778,19 @@
         <v>1940</v>
       </c>
       <c r="E92" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F92">
         <v>1940</v>
       </c>
       <c r="G92" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H92" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I92" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -21996,7 +21993,7 @@
         <v>165</v>
       </c>
       <c r="B93" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C93">
         <v>1828</v>
@@ -22005,19 +22002,19 @@
         <v>1910</v>
       </c>
       <c r="E93" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F93">
         <v>1895</v>
       </c>
       <c r="G93" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H93" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I93" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -22220,7 +22217,7 @@
         <v>166</v>
       </c>
       <c r="B94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C94">
         <v>1795</v>
@@ -22229,19 +22226,19 @@
         <v>1829</v>
       </c>
       <c r="E94" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F94">
         <v>1824</v>
       </c>
       <c r="G94" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H94" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I94" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J94">
         <v>1</v>
@@ -22444,7 +22441,7 @@
         <v>167</v>
       </c>
       <c r="B95" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C95">
         <v>1811</v>
@@ -22453,19 +22450,19 @@
         <v>1852</v>
       </c>
       <c r="E95" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F95">
         <v>1841</v>
       </c>
       <c r="G95" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H95" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I95" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -22668,7 +22665,7 @@
         <v>168</v>
       </c>
       <c r="B96" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96">
         <v>1927</v>
@@ -22677,19 +22674,19 @@
         <v>1982</v>
       </c>
       <c r="E96" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F96">
         <v>1957</v>
       </c>
       <c r="G96" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H96" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I96" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -22892,7 +22889,7 @@
         <v>169</v>
       </c>
       <c r="B97" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C97">
         <v>1828</v>
@@ -22901,19 +22898,19 @@
         <v>1910</v>
       </c>
       <c r="E97" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F97">
         <v>1856</v>
       </c>
       <c r="G97" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H97" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I97" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -23116,28 +23113,28 @@
         <v>170</v>
       </c>
       <c r="B98" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C98">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D98">
         <v>1936</v>
       </c>
       <c r="E98" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F98">
         <v>1906</v>
       </c>
       <c r="G98" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H98" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I98" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J98">
         <v>1</v>
@@ -23340,28 +23337,28 @@
         <v>171</v>
       </c>
       <c r="B99" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C99">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D99">
         <v>1936</v>
       </c>
       <c r="E99" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F99">
         <v>1922</v>
       </c>
       <c r="G99" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H99" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I99" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -23564,7 +23561,7 @@
         <v>172</v>
       </c>
       <c r="B100" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C100">
         <v>1745</v>
@@ -23573,19 +23570,19 @@
         <v>1792</v>
       </c>
       <c r="E100" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F100">
         <v>1782</v>
       </c>
       <c r="G100" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H100" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I100" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -23788,7 +23785,7 @@
         <v>173</v>
       </c>
       <c r="B101" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C101">
         <v>1893</v>
@@ -23797,19 +23794,19 @@
         <v>1930</v>
       </c>
       <c r="E101" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F101">
         <v>1921</v>
       </c>
       <c r="G101" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H101" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I101" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -24012,7 +24009,7 @@
         <v>174</v>
       </c>
       <c r="B102" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C102">
         <v>1818</v>
@@ -24021,19 +24018,19 @@
         <v>1883</v>
       </c>
       <c r="E102" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F102">
         <v>1850</v>
       </c>
       <c r="G102" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H102" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I102" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -24236,7 +24233,7 @@
         <v>175</v>
       </c>
       <c r="B103" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C103">
         <v>1870</v>
@@ -24245,19 +24242,19 @@
         <v>1953</v>
       </c>
       <c r="E103" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F103">
         <v>1915</v>
       </c>
       <c r="G103" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H103" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I103" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -24460,7 +24457,7 @@
         <v>176</v>
       </c>
       <c r="B104" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C104">
         <v>1828</v>
@@ -24469,19 +24466,19 @@
         <v>1910</v>
       </c>
       <c r="E104" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F104">
         <v>1886</v>
       </c>
       <c r="G104" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H104" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I104" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -24684,7 +24681,7 @@
         <v>177</v>
       </c>
       <c r="B105" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C105">
         <v>1860</v>
@@ -24693,19 +24690,19 @@
         <v>1904</v>
       </c>
       <c r="E105" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F105">
         <v>1896</v>
       </c>
       <c r="G105" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H105" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I105" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -24908,7 +24905,7 @@
         <v>178</v>
       </c>
       <c r="B106" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C106">
         <v>1799</v>
@@ -24917,19 +24914,19 @@
         <v>1837</v>
       </c>
       <c r="E106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F106">
         <v>1830</v>
       </c>
       <c r="G106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I106" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -25132,7 +25129,7 @@
         <v>179</v>
       </c>
       <c r="B107" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C107">
         <v>1853</v>
@@ -25141,19 +25138,19 @@
         <v>1921</v>
       </c>
       <c r="E107" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F107">
         <v>1886</v>
       </c>
       <c r="G107" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H107" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I107" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -25356,7 +25353,7 @@
         <v>180</v>
       </c>
       <c r="B108" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C108">
         <v>1811</v>
@@ -25365,19 +25362,19 @@
         <v>1852</v>
       </c>
       <c r="E108" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F108">
         <v>1834</v>
       </c>
       <c r="G108" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H108" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I108" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -25580,7 +25577,7 @@
         <v>181</v>
       </c>
       <c r="B109" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C109">
         <v>1818</v>
@@ -25589,19 +25586,19 @@
         <v>1883</v>
       </c>
       <c r="E109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F109">
         <v>1858</v>
       </c>
       <c r="G109" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H109" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I109" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J109">
         <v>1</v>
@@ -25804,7 +25801,7 @@
         <v>182</v>
       </c>
       <c r="B110" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C110">
         <v>1884</v>
@@ -25813,19 +25810,19 @@
         <v>1937</v>
       </c>
       <c r="E110" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F110">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="G110" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H110" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I110" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J110">
         <v>1</v>
@@ -26028,7 +26025,7 @@
         <v>183</v>
       </c>
       <c r="B111" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C111">
         <v>1821</v>
@@ -26037,19 +26034,19 @@
         <v>1881</v>
       </c>
       <c r="E111" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F111">
         <v>1848</v>
       </c>
       <c r="G111" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H111" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I111" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J111">
         <v>1</v>
@@ -26252,7 +26249,7 @@
         <v>184</v>
       </c>
       <c r="B112" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C112">
         <v>1821</v>
@@ -26261,19 +26258,19 @@
         <v>1891</v>
       </c>
       <c r="E112" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F112">
         <v>1857</v>
       </c>
       <c r="G112" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H112" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I112" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -26476,7 +26473,7 @@
         <v>185</v>
       </c>
       <c r="B113" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C113">
         <v>1860</v>
@@ -26485,19 +26482,19 @@
         <v>1904</v>
       </c>
       <c r="E113" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F113">
         <v>1897</v>
       </c>
       <c r="G113" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H113" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -26700,7 +26697,7 @@
         <v>186</v>
       </c>
       <c r="B114" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C114">
         <v>1823</v>
@@ -26709,19 +26706,19 @@
         <v>1886</v>
       </c>
       <c r="E114" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F114">
         <v>1859</v>
       </c>
       <c r="G114" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H114" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I114" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -26924,7 +26921,7 @@
         <v>187</v>
       </c>
       <c r="B115" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C115">
         <v>1766</v>
@@ -26933,19 +26930,19 @@
         <v>1826</v>
       </c>
       <c r="E115" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F115">
         <v>1792</v>
       </c>
       <c r="G115" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H115" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I115" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J115">
         <v>1</v>
@@ -27148,7 +27145,7 @@
         <v>188</v>
       </c>
       <c r="B116" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C116">
         <v>1821</v>
@@ -27157,19 +27154,19 @@
         <v>1881</v>
       </c>
       <c r="E116" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F116">
         <v>1846</v>
       </c>
       <c r="G116" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H116" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I116" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J116">
         <v>1</v>
@@ -27372,7 +27369,7 @@
         <v>189</v>
       </c>
       <c r="B117" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C117">
         <v>1918</v>
@@ -27381,19 +27378,19 @@
         <v>2008</v>
       </c>
       <c r="E117" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F117">
         <v>1965</v>
       </c>
       <c r="G117" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H117" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I117" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J117">
         <v>1</v>
@@ -27596,7 +27593,7 @@
         <v>190</v>
       </c>
       <c r="B118" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C118">
         <v>1818</v>
@@ -27605,19 +27602,19 @@
         <v>1883</v>
       </c>
       <c r="E118" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F118">
         <v>1862</v>
       </c>
       <c r="G118" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H118" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I118" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -27820,7 +27817,7 @@
         <v>191</v>
       </c>
       <c r="B119" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C119">
         <v>1828</v>
@@ -27829,19 +27826,19 @@
         <v>1910</v>
       </c>
       <c r="E119" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F119">
         <v>1898</v>
       </c>
       <c r="G119" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H119" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I119" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -28044,7 +28041,7 @@
         <v>192</v>
       </c>
       <c r="B120" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C120">
         <v>1811</v>
@@ -28053,19 +28050,19 @@
         <v>1852</v>
       </c>
       <c r="E120" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F120">
         <v>1835</v>
       </c>
       <c r="G120" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H120" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I120" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -28268,7 +28265,7 @@
         <v>193</v>
       </c>
       <c r="B121" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C121">
         <v>1880</v>
@@ -28277,19 +28274,19 @@
         <v>1934</v>
       </c>
       <c r="E121" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F121">
         <v>1912</v>
       </c>
       <c r="G121" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H121" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I121" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -28492,28 +28489,28 @@
         <v>194</v>
       </c>
       <c r="B122" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C122">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D122">
         <v>1936</v>
       </c>
       <c r="E122" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F122">
         <v>1901</v>
       </c>
       <c r="G122" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H122" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I122" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -28716,7 +28713,7 @@
         <v>195</v>
       </c>
       <c r="B123" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C123">
         <v>1823</v>
@@ -28725,19 +28722,19 @@
         <v>1886</v>
       </c>
       <c r="E123" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F123">
         <v>1857</v>
       </c>
       <c r="G123" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H123" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I123" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -28940,7 +28937,7 @@
         <v>196</v>
       </c>
       <c r="B124" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C124">
         <v>1811</v>
@@ -28949,19 +28946,19 @@
         <v>1852</v>
       </c>
       <c r="E124" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F124">
         <v>1842</v>
       </c>
       <c r="G124" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H124" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I124" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -29164,7 +29161,7 @@
         <v>197</v>
       </c>
       <c r="B125" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C125">
         <v>1918</v>
@@ -29173,19 +29170,19 @@
         <v>2008</v>
       </c>
       <c r="E125" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F125">
         <v>1963</v>
       </c>
       <c r="G125" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H125" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I125" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -29388,7 +29385,7 @@
         <v>198</v>
       </c>
       <c r="B126" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C126">
         <v>1918</v>
@@ -29397,19 +29394,19 @@
         <v>2008</v>
       </c>
       <c r="E126" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F126">
         <v>1960</v>
       </c>
       <c r="G126" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H126" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I126" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -29612,7 +29609,7 @@
         <v>199</v>
       </c>
       <c r="B127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C127">
         <v>1923</v>
@@ -29621,19 +29618,19 @@
         <v>1983</v>
       </c>
       <c r="E127" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F127">
         <v>1960</v>
       </c>
       <c r="G127" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H127" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I127" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J127">
         <v>1</v>
@@ -29836,7 +29833,7 @@
         <v>200</v>
       </c>
       <c r="B128" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C128">
         <v>1811</v>
@@ -29845,19 +29842,19 @@
         <v>1852</v>
       </c>
       <c r="E128" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F128">
         <v>1835</v>
       </c>
       <c r="G128" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H128" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I128" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J128">
         <v>1</v>
@@ -30060,7 +30057,7 @@
         <v>201</v>
       </c>
       <c r="B129" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C129">
         <v>1811</v>
@@ -30069,19 +30066,19 @@
         <v>1852</v>
       </c>
       <c r="E129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F129">
         <v>1835</v>
       </c>
       <c r="G129" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H129" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I129" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -30284,7 +30281,7 @@
         <v>202</v>
       </c>
       <c r="B130" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C130">
         <v>1811</v>
@@ -30293,19 +30290,19 @@
         <v>1852</v>
       </c>
       <c r="E130" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F130">
         <v>1835</v>
       </c>
       <c r="G130" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H130" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I130" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -30508,7 +30505,7 @@
         <v>203</v>
       </c>
       <c r="B131" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C131">
         <v>1880</v>
@@ -30517,19 +30514,19 @@
         <v>1921</v>
       </c>
       <c r="E131" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F131">
         <v>1914</v>
       </c>
       <c r="G131" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H131" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -30732,7 +30729,7 @@
         <v>204</v>
       </c>
       <c r="B132" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C132">
         <v>1818</v>
@@ -30741,19 +30738,19 @@
         <v>1883</v>
       </c>
       <c r="E132" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F132">
         <v>1850</v>
       </c>
       <c r="G132" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H132" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I132" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -30956,7 +30953,7 @@
         <v>205</v>
       </c>
       <c r="B133" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C133">
         <v>1893</v>
@@ -30965,19 +30962,19 @@
         <v>1930</v>
       </c>
       <c r="E133" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F133">
         <v>1929</v>
       </c>
       <c r="G133" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H133" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I133" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -31180,7 +31177,7 @@
         <v>206</v>
       </c>
       <c r="B134" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C134">
         <v>1897</v>
@@ -31189,19 +31186,19 @@
         <v>1986</v>
       </c>
       <c r="E134" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F134">
         <v>1928</v>
       </c>
       <c r="G134" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H134" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I134" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -31404,7 +31401,7 @@
         <v>207</v>
       </c>
       <c r="B135" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C135">
         <v>1894</v>
@@ -31413,19 +31410,19 @@
         <v>1959</v>
       </c>
       <c r="E135" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F135">
         <v>1924</v>
       </c>
       <c r="G135" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H135" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I135" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J135">
         <v>1</v>
@@ -31628,7 +31625,7 @@
         <v>208</v>
       </c>
       <c r="B136" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C136">
         <v>1828</v>
@@ -31637,19 +31634,19 @@
         <v>1889</v>
       </c>
       <c r="E136" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F136">
         <v>1862</v>
       </c>
       <c r="G136" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H136" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I136" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J136">
         <v>1</v>
@@ -31852,7 +31849,7 @@
         <v>209</v>
       </c>
       <c r="B137" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C137">
         <v>1821</v>
@@ -31861,19 +31858,19 @@
         <v>1891</v>
       </c>
       <c r="E137" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F137">
         <v>1869</v>
       </c>
       <c r="G137" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H137" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I137" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J137">
         <v>1</v>
@@ -32076,7 +32073,7 @@
         <v>210</v>
       </c>
       <c r="B138" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C138">
         <v>1828</v>
@@ -32085,19 +32082,19 @@
         <v>1910</v>
       </c>
       <c r="E138" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F138">
         <v>1855</v>
       </c>
       <c r="G138" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H138" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I138" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -32300,7 +32297,7 @@
         <v>211</v>
       </c>
       <c r="B139" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C139">
         <v>1828</v>
@@ -32309,19 +32306,19 @@
         <v>1910</v>
       </c>
       <c r="E139" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F139">
         <v>1899</v>
       </c>
       <c r="G139" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H139" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I139" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J139">
         <v>1</v>
@@ -32524,7 +32521,7 @@
         <v>212</v>
       </c>
       <c r="B140" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C140">
         <v>1811</v>
@@ -32533,19 +32530,19 @@
         <v>1852</v>
       </c>
       <c r="E140" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F140">
         <v>1836</v>
       </c>
       <c r="G140" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H140" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I140" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -32748,7 +32745,7 @@
         <v>213</v>
       </c>
       <c r="B141" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C141">
         <v>1818</v>
@@ -32757,19 +32754,19 @@
         <v>1883</v>
       </c>
       <c r="E141" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F141">
         <v>1855</v>
       </c>
       <c r="G141" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H141" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I141" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J141">
         <v>1</v>
@@ -32972,7 +32969,7 @@
         <v>214</v>
       </c>
       <c r="B142" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C142">
         <v>1930</v>
@@ -32981,19 +32978,19 @@
         <v>1995</v>
       </c>
       <c r="E142" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F142">
         <v>1965</v>
       </c>
       <c r="G142" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H142" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I142" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -33196,7 +33193,7 @@
         <v>215</v>
       </c>
       <c r="B143" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C143">
         <v>1860</v>
@@ -33205,19 +33202,19 @@
         <v>1904</v>
       </c>
       <c r="E143" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F143">
-        <v>1862</v>
+        <v>1892</v>
       </c>
       <c r="G143" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H143" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I143" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -33420,7 +33417,7 @@
         <v>216</v>
       </c>
       <c r="B144" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C144">
         <v>1871</v>
@@ -33429,19 +33426,19 @@
         <v>1919</v>
       </c>
       <c r="E144" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F144">
         <v>1908</v>
       </c>
       <c r="G144" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H144" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I144" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -33644,7 +33641,7 @@
         <v>217</v>
       </c>
       <c r="B145" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C145">
         <v>1905</v>
@@ -33653,19 +33650,19 @@
         <v>1973</v>
       </c>
       <c r="E145" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F145">
         <v>1955</v>
       </c>
       <c r="G145" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H145" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I145" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -33868,7 +33865,7 @@
         <v>218</v>
       </c>
       <c r="B146" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C146">
         <v>1924</v>
@@ -33877,19 +33874,19 @@
         <v>2020</v>
       </c>
       <c r="E146" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F146">
         <v>1962</v>
       </c>
       <c r="G146" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H146" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I146" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -34092,7 +34089,7 @@
         <v>219</v>
       </c>
       <c r="B147" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C147">
         <v>1811</v>
@@ -34101,19 +34098,19 @@
         <v>1852</v>
       </c>
       <c r="E147" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F147">
         <v>1832</v>
       </c>
       <c r="G147" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H147" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I147" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -34316,7 +34313,7 @@
         <v>220</v>
       </c>
       <c r="B148" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C148">
         <v>1811</v>
@@ -34325,19 +34322,19 @@
         <v>1852</v>
       </c>
       <c r="E148" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F148">
         <v>1832</v>
       </c>
       <c r="G148" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H148" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I148" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J148">
         <v>0</v>
@@ -34540,7 +34537,7 @@
         <v>221</v>
       </c>
       <c r="B149" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C149">
         <v>1811</v>
@@ -34549,19 +34546,19 @@
         <v>1852</v>
       </c>
       <c r="E149" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F149">
         <v>1832</v>
       </c>
       <c r="G149" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H149" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I149" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -34764,7 +34761,7 @@
         <v>222</v>
       </c>
       <c r="B150" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C150">
         <v>1811</v>
@@ -34773,19 +34770,19 @@
         <v>1852</v>
       </c>
       <c r="E150" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F150">
         <v>1832</v>
       </c>
       <c r="G150" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H150" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I150" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -34988,7 +34985,7 @@
         <v>223</v>
       </c>
       <c r="B151" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C151">
         <v>1828</v>
@@ -34997,19 +34994,19 @@
         <v>1910</v>
       </c>
       <c r="E151" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F151">
         <v>1889</v>
       </c>
       <c r="G151" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H151" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J151">
         <v>1</v>
@@ -35212,7 +35209,7 @@
         <v>224</v>
       </c>
       <c r="B152" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C152">
         <v>1853</v>
@@ -35221,19 +35218,19 @@
         <v>1921</v>
       </c>
       <c r="E152" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F152">
         <v>1883</v>
       </c>
       <c r="G152" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H152" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I152" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J152">
         <v>0</v>
@@ -35436,7 +35433,7 @@
         <v>225</v>
       </c>
       <c r="B153" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C153">
         <v>1821</v>
@@ -35445,19 +35442,19 @@
         <v>1881</v>
       </c>
       <c r="E153" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F153">
         <v>1864</v>
       </c>
       <c r="G153" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H153" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I153" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -35660,7 +35657,7 @@
         <v>226</v>
       </c>
       <c r="B154" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C154">
         <v>1821</v>
@@ -35669,19 +35666,19 @@
         <v>1881</v>
       </c>
       <c r="E154" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F154">
         <v>1861</v>
       </c>
       <c r="G154" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H154" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -35884,7 +35881,7 @@
         <v>227</v>
       </c>
       <c r="B155" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C155">
         <v>1860</v>
@@ -35893,19 +35890,19 @@
         <v>1904</v>
       </c>
       <c r="E155" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F155">
         <v>1888</v>
       </c>
       <c r="G155" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H155" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I155" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -36108,7 +36105,7 @@
         <v>228</v>
       </c>
       <c r="B156" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C156">
         <v>1811</v>
@@ -36117,19 +36114,19 @@
         <v>1852</v>
       </c>
       <c r="E156" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F156">
         <v>1842</v>
       </c>
       <c r="G156" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H156" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I156" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J156">
         <v>1</v>
@@ -36332,28 +36329,28 @@
         <v>229</v>
       </c>
       <c r="B157" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C157">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D157">
         <v>1936</v>
       </c>
       <c r="E157" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F157">
         <v>1895</v>
       </c>
       <c r="G157" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H157" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I157" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -36556,7 +36553,7 @@
         <v>230</v>
       </c>
       <c r="B158" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C158">
         <v>1905</v>
@@ -36565,19 +36562,19 @@
         <v>1984</v>
       </c>
       <c r="E158" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F158">
         <v>1932</v>
       </c>
       <c r="G158" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H158" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I158" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -36780,7 +36777,7 @@
         <v>231</v>
       </c>
       <c r="B159" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C159">
         <v>1818</v>
@@ -36789,19 +36786,19 @@
         <v>1883</v>
       </c>
       <c r="E159" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F159">
         <v>1877</v>
       </c>
       <c r="G159" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H159" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I159" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -37004,28 +37001,28 @@
         <v>232</v>
       </c>
       <c r="B160" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C160">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D160">
         <v>1936</v>
       </c>
       <c r="E160" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F160">
         <v>1899</v>
       </c>
       <c r="G160" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H160" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I160" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -37228,7 +37225,7 @@
         <v>233</v>
       </c>
       <c r="B161" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C161">
         <v>1905</v>
@@ -37237,19 +37234,19 @@
         <v>1964</v>
       </c>
       <c r="E161" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F161">
         <v>1960</v>
       </c>
       <c r="G161" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H161" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I161" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -37452,7 +37449,7 @@
         <v>234</v>
       </c>
       <c r="B162" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C162">
         <v>1923</v>
@@ -37461,19 +37458,19 @@
         <v>1983</v>
       </c>
       <c r="E162" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F162">
         <v>1960</v>
       </c>
       <c r="G162" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H162" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I162" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J162">
         <v>0</v>
@@ -37676,7 +37673,7 @@
         <v>235</v>
       </c>
       <c r="B163" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C163">
         <v>1860</v>
@@ -37685,19 +37682,19 @@
         <v>1904</v>
       </c>
       <c r="E163" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F163">
         <v>1900</v>
       </c>
       <c r="G163" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H163" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I163" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -37900,28 +37897,28 @@
         <v>236</v>
       </c>
       <c r="B164" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C164">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D164">
         <v>1936</v>
       </c>
       <c r="E164" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F164">
         <v>1935</v>
       </c>
       <c r="G164" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H164" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I164" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -38124,7 +38121,7 @@
         <v>237</v>
       </c>
       <c r="B165" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C165">
         <v>1818</v>
@@ -38133,19 +38130,19 @@
         <v>1883</v>
       </c>
       <c r="E165" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F165">
         <v>1859</v>
       </c>
       <c r="G165" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H165" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I165" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J165">
         <v>1</v>
@@ -38348,7 +38345,7 @@
         <v>238</v>
       </c>
       <c r="B166" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C166">
         <v>1925</v>
@@ -38357,19 +38354,19 @@
         <v>1997</v>
       </c>
       <c r="E166" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F166">
         <v>1961</v>
       </c>
       <c r="G166" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H166" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I166" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J166">
         <v>1</v>
@@ -38572,7 +38569,7 @@
         <v>239</v>
       </c>
       <c r="B167" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C167">
         <v>1904</v>
@@ -38581,19 +38578,19 @@
         <v>1977</v>
       </c>
       <c r="E167" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F167">
         <v>1967</v>
       </c>
       <c r="G167" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H167" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I167" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -38796,7 +38793,7 @@
         <v>240</v>
       </c>
       <c r="B168" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C168">
         <v>1870</v>
@@ -38805,19 +38802,19 @@
         <v>1953</v>
       </c>
       <c r="E168" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F168">
         <v>1927</v>
       </c>
       <c r="G168" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H168" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I168" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J168">
         <v>1</v>
@@ -39017,10 +39014,10 @@
     </row>
     <row r="169" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C169">
         <v>1620</v>
@@ -39029,19 +39026,19 @@
         <v>1682</v>
       </c>
       <c r="E169" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F169">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="G169" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H169" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I169" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -39241,31 +39238,31 @@
     </row>
     <row r="170" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B170" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C170">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="D170">
         <v>1936</v>
       </c>
       <c r="E170" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F170">
         <v>1931</v>
       </c>
       <c r="G170" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H170" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I170" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J170">
         <v>0</v>
@@ -39465,10 +39462,10 @@
     </row>
     <row r="171" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B171" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C171">
         <v>1899</v>
@@ -39477,19 +39474,19 @@
         <v>1951</v>
       </c>
       <c r="E171" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F171">
         <v>1926</v>
       </c>
       <c r="G171" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H171" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I171" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -39689,10 +39686,10 @@
     </row>
     <row r="172" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B172" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C172">
         <v>1915</v>
@@ -39701,19 +39698,19 @@
         <v>1979</v>
       </c>
       <c r="E172" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F172">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="G172" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H172" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I172" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -39913,10 +39910,10 @@
     </row>
     <row r="173" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B173" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C173">
         <v>1749</v>
@@ -39925,19 +39922,19 @@
         <v>1802</v>
       </c>
       <c r="E173" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F173">
         <v>1789</v>
       </c>
       <c r="G173" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H173" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I173" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -40137,10 +40134,10 @@
     </row>
     <row r="174" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B174" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C174">
         <v>1877</v>
@@ -40149,19 +40146,19 @@
         <v>1957</v>
       </c>
       <c r="E174" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F174">
-        <v>1957</v>
+        <v>1951</v>
       </c>
       <c r="G174" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H174" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I174" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J174">
         <v>0</v>
